--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,44 +461,44 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
@@ -511,22 +511,62 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_6</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
@@ -558,52 +598,68 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>A5aLmv3S</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>lassiter ariel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>tfzJeW8h</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>martinez josef</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>EHyj8Rwo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>mitchell roald</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Chep7XVi</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ngoma serge</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2RlHwfAS</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>stroud peter</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -617,28 +673,28 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>GxlXiF6D</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>halliday michael</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>GSrqbotH</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>reid brown tahir</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -647,6 +703,14 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -666,12 +730,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lAh68Xxm</t>
+          <t>0892INjM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>benteke christian</t>
+          <t>birnbaum steven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -686,34 +750,74 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cj6yFHA1</t>
+          <t>U9y2jka5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>wolff tyler</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>vPuxSnSS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>mosquera edwin</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>2FxnqFUC</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>mcvey christopher</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Mc2UiGHB</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>slisz bartosza</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -753,50 +857,74 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>KrSC9Fhb</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>gomez diego</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>nmEIaKrM</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>bush evan</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>KrSC9Fhb</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>gomez diego</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
+          <t>vgOOdZbd</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>messi lionel</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>nBxbbXjd</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>robinson robbie</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>d2xu7eXs</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>ruiz david</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dUShzrBp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>suarez luis</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -806,56 +934,120 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>bRSLQpm3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>johnson sean</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nT1BbXIh</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>laryea richie</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>z3epw0ga</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>o neill shane</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KtKzNinp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>osorio jonathan</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A3YJH5zr</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>gaines julian</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mupyf1oM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>godoy anibal</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>KGSWnoI0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>leal randall</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>GY24D9os</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>servania brandon</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KGSWnoI0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>leal randall</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>UXv2usbH</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>macnaughton lukas</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>EkrhE4VR</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>moore shaquell</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>WYtXt0RH</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>shaffelburg jacob</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -863,50 +1055,98 @@
           <t>MTkoJCzn</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29yL8IQ9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>baird corey</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>xtm44hb9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>miazga matthew</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>S0jteiei</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>robinson miles</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>UsBqE6t9</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>bedoya alejandro</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Ewo9UCjb</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>leflore isaiah</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ji2vQ3vP</t>
+          <t>ABzjRFre</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>trent holden</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>blake andre</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dlj9zaWb</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>gazdag daniel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Ewo9UCjb</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>leflore isaiah</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8tHxTMze</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>martinez jose</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -920,28 +1160,28 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>AymTlL8c</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>dellavalle lorenzo</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>v5AXXftj</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>martinez david</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -950,6 +1190,14 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -987,44 +1235,52 @@
           <t>velasco alan</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>p0fLP0ug</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>bacharach hugo</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>KIN4ChMN</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>nyeman moses</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>zRVPjolD</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>reynoso emanuel</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1046,18 +1302,18 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>rgEPHjOC</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>arreaga xavier</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1068,6 +1324,14 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1097,52 +1361,60 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>APPpO179</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>bonilla jose</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0laOLfLr</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>holt erik</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>fZM0WV7l</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>ruiz pablo</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>8dMNjLjD</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>silva marcelo</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1156,28 +1428,28 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>O2OHmuib</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>chacon daniel</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>nXphGKf9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>stewart baynes kimani</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1186,6 +1458,140 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>l8BtS6uD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>brugman gaston</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>GbuDhihD</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>hope gund rio</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>dYQXlhHM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ilenic mitja</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AVAn8mrG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>daniel</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08UQE1DR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>COWIPrGB</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>loria marvin</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,74 +441,74 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
@@ -521,131 +521,69 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_7</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_7</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_8</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_8</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YsPPQKfU</t>
+          <t>nmEIaKrM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>campbell george</t>
+          <t>bush evan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0QDAVSZp</t>
+          <t>Krqp3vSl</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>jabang ousman</t>
+          <t>ford kortne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A5aLmv3S</t>
+          <t>4j77gmDr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lassiter ariel</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>tfzJeW8h</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>martinez josef</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>EHyj8Rwo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>mitchell roald</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Chep7XVi</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ngoma serge</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2RlHwfAS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>stroud peter</t>
-        </is>
-      </c>
+          <t>ndenbe logan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -654,49 +592,75 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ENyQYY5d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>antley william</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0892INjM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>birnbaum steven</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>GxlXiF6D</t>
+          <t>pMh10sbj</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>halliday michael</t>
+          <t>canouse russell</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GSrqbotH</t>
+          <t>U9y2jka5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>reid brown tahir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2FxnqFUC</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>mcvey christopher</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -705,174 +669,154 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENyQYY5d</t>
+          <t>29yL8IQ9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>antley william</t>
+          <t>baird corey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0892INjM</t>
+          <t>G6fhkE8g</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>birnbaum steven</t>
+          <t>bye brandon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pMh10sbj</t>
+          <t>rorJXVFH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>canouse russell</t>
+          <t>chancalay tomas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>U9y2jka5</t>
+          <t>xtm44hb9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>hopkins jackson</t>
+          <t>miazga matthew</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8xa2tgyo</t>
+          <t>S0jteiei</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>abram luis</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SEHVGTmg</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lobjanidze saba</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>vPuxSnSS</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>mosquera edwin</t>
-        </is>
-      </c>
+          <t>robinson miles</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2FxnqFUC</t>
+          <t>bcUmtA2T</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>mcvey christopher</t>
+          <t>gil ignacio</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Mc2UiGHB</t>
+          <t>G4sqpfJn</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>slisz bartosza</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>mcnamara thomas</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Me4woTz5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>spaulding ryan</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4pT7GbXj</t>
+          <t>EHyj8Rwo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>aviles tomas</t>
+          <t>mitchell roald</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4nPbkFeS</t>
+          <t>bRSLQpm3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>farias facundo</t>
+          <t>johnson sean</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>drwnu3ZE</t>
+          <t>nT1BbXIh</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>freire nicolas</t>
+          <t>laryea richie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KrSC9Fhb</t>
+          <t>Chep7XVi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>gomez diego</t>
+          <t>ngoma serge</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>nmEIaKrM</t>
+          <t>2RlHwfAS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>bush evan</t>
+          <t>stroud peter</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -881,307 +825,225 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>vgOOdZbd</t>
+          <t>z3epw0ga</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>messi lionel</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>o neill shane</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>KtKzNinp</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>osorio jonathan</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>nBxbbXjd</t>
+          <t>GY24D9os</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>robinson robbie</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>d2xu7eXs</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>ruiz david</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dUShzrBp</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>suarez luis</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>servania brandon</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bRSLQpm3</t>
+          <t>GxlXiF6D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>johnson sean</t>
+          <t>halliday michael</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nT1BbXIh</t>
+          <t>fRhphq6i</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>laryea richie</t>
+          <t>gasper chase</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>z3epw0ga</t>
+          <t>QJrUSjEf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>o neill shane</t>
+          <t>gutman andrew</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KtKzNinp</t>
+          <t>GSrqbotH</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>osorio jonathan</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>A3YJH5zr</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>gaines julian</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Mupyf1oM</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>godoy anibal</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>KGSWnoI0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>leal randall</t>
-        </is>
-      </c>
+          <t>reid brown tahir</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>GY24D9os</t>
+          <t>fqzwMb0n</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>servania brandon</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>UXv2usbH</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>macnaughton lukas</t>
-        </is>
-      </c>
+          <t>salquist tobias</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>EkrhE4VR</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>moore shaquell</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>WYtXt0RH</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>shaffelburg jacob</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29yL8IQ9</t>
+          <t>UsBqE6t9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>baird corey</t>
+          <t>bedoya alejandro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>xtm44hb9</t>
+          <t>juUdUvvS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>miazga matthew</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>S0jteiei</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>robinson miles</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>arfield scott</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ABzjRFre</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>blake andre</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UsBqE6t9</t>
+          <t>dlj9zaWb</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>bedoya alejandro</t>
+          <t>gazdag daniel</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ABzjRFre</t>
+          <t>Ewo9UCjb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>blake andre</t>
+          <t>leflore isaiah</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>dlj9zaWb</t>
+          <t>8tHxTMze</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>gazdag daniel</t>
+          <t>martinez jose</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Ewo9UCjb</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>leflore isaiah</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8tHxTMze</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>martinez jose</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>p0fLP0ug</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bacharach hugo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>jZ9TQ59s</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>valencia jhojan</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>AymTlL8c</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>v5AXXftj</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>martinez david</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>zRVPjolD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>reynoso emanuel</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1192,79 +1054,73 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2BYxcCoI</t>
+          <t>A3YJH5zr</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>geovane jesus</t>
+          <t>gaines julian</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ngsoZ62f</t>
+          <t>GbuDhihD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>pomykal paxton</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ELzAby5L</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>velasco alan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>hope gund rio</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mupyf1oM</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>godoy anibal</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>p0fLP0ug</t>
+          <t>KGSWnoI0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>bacharach hugo</t>
+          <t>leal randall</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>KIN4ChMN</t>
+          <t>UXv2usbH</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>nyeman moses</t>
+          <t>macnaughton lukas</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>zRVPjolD</t>
+          <t>EkrhE4VR</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>reynoso emanuel</t>
+          <t>moore shaquell</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1273,185 +1129,215 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>WYtXt0RH</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>shaffelburg jacob</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SdBJUCMo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quinones nelson</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CSKGShgi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>almada thiago</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>rgEPHjOC</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>arreaga xavier</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>vPuxSnSS</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>mosquera edwin</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Mc2UiGHB</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>slisz bartosza</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Krqp3vSl</t>
+          <t>O2OHmuib</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ford kortne</t>
+          <t>chacon daniel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4j77gmDr</t>
+          <t>0QDAVSZp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ndenbe logan</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>APPpO179</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>bonilla jose</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0laOLfLr</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>holt erik</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>fZM0WV7l</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>ruiz pablo</t>
-        </is>
-      </c>
+          <t>jabang ousman</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>A5aLmv3S</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lassiter ariel</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nXphGKf9</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>stewart baynes kimani</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>8dMNjLjD</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>silva marcelo</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>APPpO179</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bonilla jose</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>l8BtS6uD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>brugman gaston</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0laOLfLr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>holt erik</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O2OHmuib</t>
+          <t>fZM0WV7l</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>chacon daniel</t>
+          <t>ruiz pablo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>nXphGKf9</t>
+          <t>8dMNjLjD</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>stewart baynes kimani</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>silva marcelo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>K8nVgpfL</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vera brayan</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1460,120 +1346,116 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>l8BtS6uD</t>
+          <t>AymTlL8c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>brugman gaston</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AVAn8mrG</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>daniel</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>v5AXXftj</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>martinez david</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>GbuDhihD</t>
+          <t>M9UPk5L5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>hope gund rio</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>dYQXlhHM</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ilenic mitja</t>
-        </is>
-      </c>
+          <t>tillman timothy</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>08UQE1DR</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AVAn8mrG</t>
+          <t>COWIPrGB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>daniel</t>
+          <t>loria marvin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>v5gGA3R2</t>
+          <t>29H9TmUe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>marcinkowski jt</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>08UQE1DR</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ricketts jamar</t>
-        </is>
-      </c>
+          <t>adekugbe sam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>COWIPrGB</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>loria marvin</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1586,12 +1468,59 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ELzAby5L</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>velasco alan</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -801,26 +801,34 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>hfxD47ea</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>morgan lewis</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Chep7XVi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ngoma serge</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2RlHwfAS</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>stroud peter</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -864,46 +872,54 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>lGn3Qr31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>brekalo david</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fRhphq6i</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>gasper chase</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>QJrUSjEf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>gutman andrew</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>GxlXiF6D</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>halliday michael</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>fRhphq6i</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>gasper chase</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>QJrUSjEf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>gutman andrew</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>GSrqbotH</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>reid brown tahir</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -918,8 +934,16 @@
           <t>salquist tobias</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CKcCpcKN</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>shaqiri xherdan</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,6 +1546,789 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,789 +1546,6 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>jqf7smJ3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>G0IRHiWk</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiHVGBod</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4nbBt7Y9</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>b9cFuRmG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zZKrObIr</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hAFmNIXl</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QNDeLd21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>W0EiMxme</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>xbHaKGH7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>v3erq0f8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IgfnrK9E</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>nTbjsvPK</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YyTMIXGq</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,118 +425,528 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
@@ -548,50 +958,452 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>IJv9ax1Q</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>schulte patrick</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zk4qsEuM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>moreira steven</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QganPGYI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>camacho rudy</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>f5qxQepJ</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cheberko yevgen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AqWyTfI5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>farsi mohamed</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SOGHjAs1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nagbe darlington</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>pYFMERNj</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>morris aidan</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Y7TZabC7</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>arfsten maximilian</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>nmxk6R3j</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ramirez christian</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>f3AIj6Gd</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>rossi diego</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>65KF7LTO</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>cucho hernandez</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>rigYeglk</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>pulskamp john</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>AXTrLxoE</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>castellanos robert</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>OhJpD8Re</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rosero daniel</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0hL9u1Ls</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>voloder robert</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8nD2RzEl</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>pierre kayden</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>xSX2CDIn</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rodriguez memo</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>p0TRjzSa</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>radoja nemanja</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>CSKL6HMI</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>bassong zohran</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>QN2WPSVT</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>thommy erik</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>A7xP1pMQ</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>agade william</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>G8OMmUIP</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>afrifa stephen</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>IVdZK6M8</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>amundsen malte</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2uFgW9QP</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>habroune taha</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>hGBjyLfE</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>hagen nicholas</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>nchpWIt5</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>hinestroza marino</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>A70Jf46M</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>jones derrick</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>A9cyouqp</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>matan alexandru</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>YueP3mZg</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>sands will</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>lMqsisyG</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>yeboah yaw</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>rH3tj2lb</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>zawadzki sean</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>fNA0X55t</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>davis jake</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>KCXGwpBP</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>fontas andreu</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>dbiLwA0E</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>melia tim</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>OlIYg590</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>rindov chris</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>hQBGGZbN</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>russell johnny</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>niMEvdKj</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>shelton khiry</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>OWahRkqH</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>tzionis marinos</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>IXSkIpz6</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>vargas alenis</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>nmEIaKrM</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>bush evan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>Krqp3vSl</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>ford kortne</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4j77gmDr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>ndenbe logan</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>GEGCHPx6</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>walter remi</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -601,74 +1413,460 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CG6Onh70</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>miller tyler</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>67iee5Vo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>herrera aaron</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ielx5NU3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tubbs garrison</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GjDwWCMo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>bartlett lucas allen</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>hG3ZBDF0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>dajome cristian</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>bu7kCxIm</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ku dipietro theodore</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>r1rFiuNe</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>peltola matti</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23FbWu7B</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>klich mateusz</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6wv4vfJ4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>rodriguez martin</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>hIw1X6PN</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>murrell jacob</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>lAh68Xxm</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>benteke christian</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>vXZC5twK</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>clark steve</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>joYyh3gO</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dorsey griffin</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>fHhXENuf</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sviatchenko erik</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>OC2EM7XJ</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>micael</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>nD7FL7I7</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>steres daniel</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>lEkgKjPO</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>artur</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>QssIzJ9S</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>herrera hector</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>WlBrB7Tg</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>blessing latif</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>AeGpgXgm</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>bassi amine</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2ZL3QFAJ</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>ibrahim aliyu</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>nLTBdvCh</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>ferreira sebastian</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>tdoa9jx7</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>akinmboni matai</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>INEwm8xA</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>bono alex</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>GpxTwfLq</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>crockford nathan</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>OUH3RyFt</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>gabriel pirani</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>h0XExJmo</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>santos pedro</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>ENuOM4Jq</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>stroud jared</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>zqhYCfjd</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>bartlow ethan</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>b7DGETog</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>escobar franco</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>pzada13b</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>gregus jan</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>Gf4tgbP3</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>kowalczyk sebastian</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0GCFbR0r</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>raines brooklyn</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>OWs5WlYu</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>schmitt tate</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>nydehH4r</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>segal gabriel</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>lzISf8BT</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>smith bradley</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>ENyQYY5d</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>antley william</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>SdBJUCMo</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>quinones nelson</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>MLKogEfa</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>tarbell andrew</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
         <is>
           <t>0892INjM</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>birnbaum steven</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>pMh10sbj</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>canouse russell</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>O8vJ4MN3</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>fletcher kristian</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
         <is>
           <t>U9y2jka5</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>hopkins jackson</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>2FxnqFUC</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>mcvey christopher</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -678,90 +1876,468 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>65qMcSsk</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>celentano roman</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EeCZfvc1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>powell alvas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ac0f6aUi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>murphy ian</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EmByTsz3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>yedlin deandre</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CERONUR9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>orellano luca</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Wb24z4qm</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bucha pavel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Qgy2DEEi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>nwobodo obinna</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ew6ZM870</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>asad yamil</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>UHAYgN9J</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>acosta luciano</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>bgmn5guC</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>kelsy kevin</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SYf84XxQ</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>valenzuela gerado</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>t2qaKiy1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>ivacic aljaz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>bgp40b4S</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>jones dejuan</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>jqg8GNsP</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>romney david</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>rgEPHjOC</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>arreaga xavier</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>x8DF5hdR</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>lima nick</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>tdzmBBpt</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>harkes ian</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vDPZngKJ</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>polster matt</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>hfGr3JtE</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>boateng ema</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>W8ixgd70</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gil carles</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>GUqdXgyQ</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>bajraktarevic esmir</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>AeAZMqTq</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>vrioni giacomo</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>KjuaVo0b</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>boupendza aaron</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>hxvYvgmQ</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>foster isaiah</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>G8J0E6NO</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>hagglund nick</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>x4GDtQAg</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>halsey bret</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>YHNlP88c</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>CM9lhfg0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>keller kipp</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>xSjv8o7m</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>kubo yuya</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>QJXMi0b1</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>pinto malik</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>nurCNCMA</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>santos sergio</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>zkeO5AoD</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>buck noel</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>G6fhkE8g</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>bye brandon</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>lOgLaOqB</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>edwards earl</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>pfMI4LWA</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>farrell andrew</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>UoFEFxwC</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>kessler henry</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>4Ax57CjI</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>mensah jonathan</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>WGKzip6I</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>panayotou jack</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>29yL8IQ9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>baird corey</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>G6fhkE8g</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>bye brandon</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>rorJXVFH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>chancalay tomas</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>bcUmtA2T</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>gil ignacio</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>G4sqpfJn</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>mcnamara thomas</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
         <is>
           <t>xtm44hb9</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>miazga matthew</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>S0jteiei</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>robinson miles</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>bcUmtA2T</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>gil ignacio</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>G4sqpfJn</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>mcnamara thomas</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr">
         <is>
           <t>Me4woTz5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>spaulding ryan</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -771,98 +2347,516 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>I7hHvjo8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>meara ryan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2opOliMF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nealis dylan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lrm5HUGk</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nealis sean</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>21LF2F5n</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>eile noah</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>KhShc534</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>tolkin john</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Kx11bv9D</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gjengaar dennis</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>M3OWSmEK</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>edelman daniel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UoAlKFVe</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>amaya frankie</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>S88XrqYl</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>carmona wikelman</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>r9KSzxIr</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>elias manoel</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>r98Hclis</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>vanzeir dante</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>p48dwOiT</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>luka gavran</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>xAK6V1ci</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>rosted sigurd</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>AH6Dnzt9</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>long kevin</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>S29QRgLo</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>gomis nickseon</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Ghmdi8ej</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>bernardeschi federico</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>YLtE6R5U</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>coello camarero alonso</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>zwOGJAV1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>flores deybi</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>jagUidH4</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>etienne derick</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>CGI0s8Kj</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>longstaff matthew</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>6qUE0AeN</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>insigne lorenzo</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>E7o31oTD</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>owusu prince</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>6k6rtKui</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>burke cory</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>8lSe4DC8</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>donkor ronald</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jkAB9GIq</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>duncan kyle</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>61JmbCV4</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>estrela bento</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>lCyxppgD</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>hall julian</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>AwQIIHlp</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>harper cameron</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>OnJtVlob</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>marcucci aj</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>CKmY1Xij</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>o connor aidan</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>rXSckKil</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>reyes andres</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Yo7zAd0f</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>franklin kobe</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>UD0q8zV6</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>kerr deandre</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>QZkWVPb4</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>mabika aime</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>UZ51tgN4</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>mailula cassius</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>rD6gr7yH</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>marshall rutty jahkeele</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>4MuW4L61</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ranjitsingh greg</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>h82m6z8F</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>staniland charlie</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>QNVzA0WJ</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>thompson kosi</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>U1vy4HGk</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>carlos coronel</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>bRSLQpm3</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>johnson sean</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>nT1BbXIh</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>laryea richie</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>z3epw0ga</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>o neill shane</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>IehILnUA</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>forsberg emil</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>EHyj8Rwo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>mitchell roald</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>bRSLQpm3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>johnson sean</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>nT1BbXIh</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>laryea richie</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>hfxD47ea</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>morgan lewis</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>Chep7XVi</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>ngoma serge</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>2RlHwfAS</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>stroud peter</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>z3epw0ga</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>o neill shane</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>KtKzNinp</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>osorio jonathan</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>GY24D9os</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>servania brandon</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>WSKByXG4</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>spicer tyrese</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -872,82 +2866,508 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>bF92gq0b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stajduhar mason</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bBmS5UX8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>thorhallsson dagur</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>t65vhYRg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>schlegel rodrigo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8OM9Vfod</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jansson robin</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6eXjEYkT</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rafael santos</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>lhAqDO8D</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>torres facundo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lOFDt82b</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>araujo cesar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>xjFz7K56</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>lodeiro nicolas</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2wLx0Osd</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>angulo ivan</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>EZEVJouA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>mcguire duncan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ltpb2uSG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>muriel luis</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>n79WXocj</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>brady chris</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>fagAWisc</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>souquet arnaud</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>GAG3nyP6</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>teran carlos</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>nX0UykbH</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>pineda mauricio</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2mWA9Y4H</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>arigoni allan</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2wPfQs28</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>herbers fabian</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>vc66Seae</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>acosta kellyn</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>dWTqQgRG</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>dean jr robert jonathan</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>z31sIFlM</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>haile selassie maren</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>hKGJC09T</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>gutierrez brian</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>EuZGz6mD</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>cuypers hugo</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>4MsxRhmb</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>felipe martins</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>xxEtrKMD</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>freeman alexander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>p8fMKT2U</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>kocevski jeorgio</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>CzMMXwgt</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>lynn jack</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>zLUoizhj</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>ojeda martin</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>ncdGec7l</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>otero javier</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>tdEFL5Su</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>rivera wilfredo</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0Mh1aQx6</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>smith kyle</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>xM5xKXk6</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>williams thomas</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>Ug6FFtjG</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>barlow tom</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>CMEMk4l7</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>casas javier</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>AuWO1Jom</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>czichos rafael</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>4MkmBF09</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>gimenez gaston</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>dzmQbSaB</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>koutsias georgios</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>Y3fj7Vhj</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>mueller chris</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>W4J0GcZ4</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>omsberg wyatt</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>8W6bELrN</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>richey spencer</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
           <t>lGn3Qr31</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>brekalo david</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>fRhphq6i</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>gasper chase</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>QJrUSjEf</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>gutman andrew</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>YBrWh9gH</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>navarro federico</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>MN3tNIu1</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>cartagena wilder</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>KCeKofNN</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>enrique ramiro</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>Ik9rz2Bn</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>gallese pedro</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
         <is>
           <t>GxlXiF6D</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>halliday michael</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>GSrqbotH</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>reid brown tahir</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>fqzwMb0n</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>salquist tobias</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>CKcCpcKN</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>shaqiri xherdan</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -957,74 +3377,476 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>fyVC7jve</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>rick andrew</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6BLphg38</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>harriel nathan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>QyCyxm0g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>glesnes jakob</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8CN7Nng2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>elliott jack</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O6htidEe</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>wagner kai</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>pK1XzKbU</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>flach leon</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>tlilbW9M</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>sullivan quinn</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>MBaUW69d</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>bueno jesus</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>I17X8gpH</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>rafanello jeremy</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8643FysN</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>uhre mikael</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>259hPT4F</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>baribo tai</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>tCYRfWGU</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>kahlina kristijan</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2Hk6Qxu3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>byrne nathan</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>YuF9dYaN</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>malanda adilson</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>d4Zg8Fa2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>privett andrew</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>U7yFa7e2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>uronen jere</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Gd5hqV7h</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>westwood ashley</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>lSODVH6K</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>bronico brandt</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>lObMfPz8</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>abada liel</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>OlGNCrIO</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>bender benjamin</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>rDL1Od4c</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>vargas kerwin</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>69kPHWm8</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>agyemang patrick</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>bVvEOY1Q</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>adeniyi markus</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>EFptvtls</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>donovan chris</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Io2gXoT8</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>makhanya olwethu</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>08Tn3g3J</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>mbaizo olivier</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>QqD1LqEi</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>mcglynn jack</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>fXpOC2k1</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>ngabo sanders</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>ABgVUsY1</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>olney jr christopher</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>zNFcpvWN</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>semmle oliver</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>IRgPjPfL</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>vazquez david</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>tfH0qS7U</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>bingham david</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>tUYikvm7</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>dejaegere brecht</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>Sdv3ugJ7</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>diani djibril</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>d6boa3Of</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>joao pedro</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>ngTfCVJB</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>lindsey jaylin</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>8WHyJFeb</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>petkovic nikola</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>YP2b3C3i</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>smalls tyger</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0lxxpom1</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>tavares iuri</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
           <t>UsBqE6t9</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>bedoya alejandro</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>juUdUvvS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>arfield scott</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>4zv75ECa</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>tuiloma bill</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
         <is>
           <t>ABzjRFre</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>blake andre</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>dlj9zaWb</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>gazdag daniel</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>Ewo9UCjb</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>leflore isaiah</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>8tHxTMze</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>martinez jose</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1032,38 +3854,14 @@
           <t>4nxtRRYM</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>p0fLP0ug</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>bacharach hugo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>jZ9TQ59s</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>valencia jhojan</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>zRVPjolD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>reynoso emanuel</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1078,6 +3876,112 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>p0fLP0ug</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>bacharach hugo</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>jZ9TQ59s</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>valencia jhojan</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>zRVPjolD</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>reynoso emanuel</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1085,84 +3989,166 @@
           <t>IktpQolT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A3YJH5zr</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>gaines julian</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GbuDhihD</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>hope gund rio</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Mupyf1oM</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>godoy anibal</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>KGSWnoI0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>leal randall</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>UXv2usbH</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>macnaughton lukas</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>EkrhE4VR</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>moore shaquell</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>A3YJH5zr</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>gaines julian</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>GbuDhihD</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>hope gund rio</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>Mupyf1oM</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>godoy anibal</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>KGSWnoI0</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>leal randall</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>EkrhE4VR</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>moore shaquell</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
         <is>
           <t>WYtXt0RH</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>shaffelburg jacob</t>
         </is>
       </c>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1172,26 +4158,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8xa2tgyo</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>abram luis</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CSKGShgi</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>almada thiago</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1200,351 +4170,136 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>SEHVGTmg</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>lobjanidze saba</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>vPuxSnSS</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>mosquera edwin</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Mc2UiGHB</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>slisz bartosza</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>O2OHmuib</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>chacon daniel</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0QDAVSZp</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>jabang ousman</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>A5aLmv3S</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lassiter ariel</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>nXphGKf9</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>stewart baynes kimani</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>APPpO179</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bonilla jose</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>l8BtS6uD</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>brugman gaston</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0laOLfLr</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>holt erik</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fZM0WV7l</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ruiz pablo</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8dMNjLjD</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>silva marcelo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>K8nVgpfL</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>vera brayan</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>AymTlL8c</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>AVAn8mrG</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>daniel</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>v5gGA3R2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>marcinkowski jt</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>v5AXXftj</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>martinez david</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>M9UPk5L5</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>tillman timothy</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>08UQE1DR</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>ricketts jamar</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>COWIPrGB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>loria marvin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>29H9TmUe</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>adekugbe sam</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2BYxcCoI</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>geovane jesus</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ngsoZ62f</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>pomykal paxton</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>ELzAby5L</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>velasco alan</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>CSKGShgi</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>almada thiago</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>vPuxSnSS</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>mosquera edwin</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>Mc2UiGHB</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>slisz bartosza</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,68 +425,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:CM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
         </is>
       </c>
     </row>
@@ -498,64 +888,438 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>dlT4erCr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lloris hugo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WWqBvVIo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>palencia sergi</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SQqkeCBr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>murillo jesus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>j7mSiM5T</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>long aaron</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>QVSaZMqo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hollingshead ryan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>M9UPk5L5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tillman timothy</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>QsikwATm</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>sanchez ilie</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>U7FsbKD2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>eduard atuesta</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bglj0vqg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bogusz mateusz</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CGwmsqmU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>kamara kei</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>h2Kyk4GC</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>bouanga denis</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>SWzpPKw5</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>jackson jacob</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>tYD2Ir6c</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>marie paul</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>UZx1nZ12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>munie daniel</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>bigivPsM</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>rodrigues</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>bThWSPHa</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>costa vitor</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>tva7h3F4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>yueill jackson</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>86yHQmhb</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>tsakiris niko</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>jLvCo8Tr</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>espinoza cristian</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>EiLC5LXi</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>lopez hernan</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>r9tK2W66</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>pellegrino amahl william</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>v5Rs2UJm</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>ebobisse jeremy</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0tfET0p0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>angel gutierrez tomas</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>b3l6SZRd</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>campos omar</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>KWuZy0ib</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>duenas erik</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>v5AXXftj</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>martinez david</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>SMYXLviA</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>musto thomas</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>dSBwgy44</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>ordaz nathan</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>vPaIjQ6l</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>romero abraham</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>SdEOp4hF</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>segura eddie</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>4lp3AS7N</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>baldisimo michael</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>CCDWJ9oJ</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>beason tanner</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Cr2jDPjr</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>judd preston</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>GdAkQWX7</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>kikanovic benjamin</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>pAVyD4bJ</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>morales alfredo</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>xQilIKol</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>skahan jack</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>2atiw4Jq</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>thompson tommy</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>nyX6YfQR</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>walls casey</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>zDM86rgI</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>yarbrough william</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>AymTlL8c</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>dellavalle lorenzo</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>v5AXXftj</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>martinez david</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>M9UPk5L5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>tillman timothy</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>AVAn8mrG</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>daniel</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>v5gGA3R2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>marcinkowski jt</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>08UQE1DR</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>ricketts jamar</t>
         </is>
       </c>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -565,40 +1329,430 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4Q1Vd5nP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pantemis james</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>prL7bcFQ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mosquera juan</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rqtL28Ik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>mcgraw zac</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8W0WzBQK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>zuparic dario</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SMy23AYh</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bravo claudio</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>U3WGsjPA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>chara diego</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>riy7xfr2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ayala david</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ALqEYOjK</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>moreno santiago</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>xpg04UIc</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>evander</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>zXhvVuhI</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>rodriguez jonathan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>djFRsOSt</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>mora felipe</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>SMi9jQFn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>takaoka yohei</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GbnFhRn9</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>brown javain</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2eOl9zqa</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>veselinovic ranko</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>SbZcWdsA</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>blackmon tristan</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>zmuN7tEa</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>laborda mathias</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>f9tMZSaG</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>berhalter sebastian</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tAgQRmS5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>vite pedro</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0MWvMpbP</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>schopf alessandro</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>hdtaItst</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>bovalina giuseppe</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>A51V8t9T</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>picault fafa</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>AebWyF4I</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>gauld ryan</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>EDpV2K92</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>antony</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>W6pvfAra</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>asprilla dairon</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>WSjxZMzk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>mabiala larrys</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0bfSS1qe</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>miller eric</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>6ei7ec9a</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>muse trey</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>KdpPcYeU</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>nathan fogaca</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>Cf1rffSI</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>paredes cristhian</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>vySEdeXs</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>williamson eryk</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>O25UBh12</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>bendik joseph</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>pCOZbM35</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>boehmer isaac</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>OAVZLEcs</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>johnson levonte</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>G6mQcrYu</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>kreilach damir</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>CIF7hP3j</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>martins luis</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>2ytqG7KO</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>mbongue ralph priso</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>S8dyrRb9</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>raposo ryan</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>neS4MpEa</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>utvik bjorn</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>lEqeFmMG</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>white brian</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>t6eNizpa</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>araujo miguel</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>29H9TmUe</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>adekugbe sam</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>COWIPrGB</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>loria marvin</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>29H9TmUe</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>adekugbe sam</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -606,40 +1760,438 @@
           <t>8K42rT3c</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IkRCT4d9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>frei stefan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UZsrETt7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>roldan cristian</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>zeu34hlq</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>gomez andrade yeimar</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>4pQfA8ui</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ragen jackson</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>UyeIXogb</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nouhou</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>YVRnyYz4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vaargas obed</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>O4TX4LC9</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>joao paulo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nDTyTCP9</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>musovski danny</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0Os9oNdD</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>rusnak albert</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>YusgQlsT</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>leo chu</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>zy3QDhFE</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>morris jordan</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>QZUlDAhp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>paes maarten</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>zPaFQZT7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>arriola paul</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>CpvYfWnT</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ibeagha sebastian</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>lnWs7qNJ</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>nkosi tafari</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>b7khARQH</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>farfan marco</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2ZREE4mC</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ntsabeleng tsiki</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>dftXOTEE</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>lletget sebastian</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>6ZmchPft</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>fraser liam</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>8EjOd1bt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>delgado patrickson</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>G0FHIX1G</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>ferreira jesus</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2JMpq78N</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>musa petar</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>rgEPHjOC</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>arreaga xavier</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>GhWbeEC5</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>baker cody</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Q7VP1SXe</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>baker whiting reed</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>dKKEm3CS</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>leyva dany</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>AyMPAqE6</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>nathan</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2L72QXjs</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>rothrock paul</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>06BxDxL0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>ruidiaz raul</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>4S22O3l4</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>teves dylan</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>OMnknAig</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>ansah eugene</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>httabn7M</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>farrington logan</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>rB26jIhb</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>gonzalez omar</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>UBJmVfdm</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>junqua sam</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>UgaTUneE</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>kamungo bernard</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>QZvQg692</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>maurer jimmy</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>MqeBl5KD</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>sainte carl</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>xfCyEHq2</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>sealy dante</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>fP18CT0m</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>twumasi emmanuel</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>2BYxcCoI</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>geovane jesus</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>ngsoZ62f</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>pomykal paxton</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>ELzAby5L</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>velasco alan</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>Uq02YxNL</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>thomas andrew</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A42"/>
+  <dimension ref="A2:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -526,195 +526,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A15"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>jqf7smJ3</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GbuDhihD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hope gund rio</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6NagVF8Q</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rodriguez santiago</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>lGn3Qr31</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>brekalo david</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MN3tNIu1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cartagena wilder</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ik9rz2Bn</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>gallese pedro</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GxlXiF6D</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>halliday michael</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GSrqbotH</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>reid brown tahir</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +583,20 @@
           <t>G0IRHiWk</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +604,20 @@
           <t>fiHVGBod</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +625,20 @@
           <t>4nbBt7Y9</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +646,20 @@
           <t>b9cFuRmG</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +667,20 @@
           <t>zZKrObIr</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +688,20 @@
           <t>hAFmNIXl</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +709,20 @@
           <t>QNDeLd21</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +730,20 @@
           <t>W0EiMxme</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +751,20 @@
           <t>xbHaKGH7</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +772,20 @@
           <t>v3erq0f8</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +793,20 @@
           <t>IgfnrK9E</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +814,20 @@
           <t>nTbjsvPK</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +835,671 @@
           <t>YyTMIXGq</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,76 @@
           <t>player_name_miss_away_5</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -576,6 +646,20 @@
           <t>reid brown tahir</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -583,20 +667,130 @@
           <t>G0IRHiWk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>zwOGJAV1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>flores deybi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bRSLQpm3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>johnson sean</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nT1BbXIh</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>laryea richie</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CGI0s8Kj</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>longstaff matthew</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>z3epw0ga</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>o neill shane</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vPuxSnSS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>mosquera edwin</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Mc2UiGHB</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>slisz bartosza</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>KtKzNinp</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>osorio jonathan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>GY24D9os</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>servania brandon</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>WSKByXG4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>spicer tyrese</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -604,20 +798,90 @@
           <t>fiHVGBod</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0QDAVSZp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jabang ousman</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A5aLmv3S</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lassiter ariel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>UsBqE6t9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>bedoya alejandro</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ABzjRFre</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>blake andre</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dlj9zaWb</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>gazdag daniel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ewo9UCjb</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>leflore isaiah</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8tHxTMze</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>martinez jose</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -625,12 +889,36 @@
           <t>4nbBt7Y9</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rorJXVFH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>chancalay tomas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bcUmtA2T</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>gil ignacio</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nmEIaKrM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>bush evan</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -639,6 +927,36 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>G4sqpfJn</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>mcnamara thomas</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Me4woTz5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>spaulding ryan</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -646,20 +964,138 @@
           <t>b9cFuRmG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>U1vy4HGk</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carlos coronel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>M3OWSmEK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>edelman daniel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>tdoa9jx7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>akinmboni matai</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ENyQYY5d</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>antley william</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>lAh68Xxm</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>benteke christian</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0892INjM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>birnbaum steven</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>pMh10sbj</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>canouse russell</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>EHyj8Rwo</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>mitchell roald</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>hfxD47ea</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>morgan lewis</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>U9y2jka5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>hopkins jackson</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2FxnqFUC</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>mcvey christopher</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Chep7XVi</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ngoma serge</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2RlHwfAS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stroud peter</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -667,20 +1103,98 @@
           <t>zZKrObIr</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>29yL8IQ9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>baird corey</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>xtm44hb9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>miazga matthew</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Qgy2DEEi</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>nwobodo obinna</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CERONUR9</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>orellano luca</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>S0jteiei</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>robinson miles</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ELzAby5L</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>velasco alan</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -688,8 +1202,16 @@
           <t>hAFmNIXl</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -702,6 +1224,20 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -709,20 +1245,138 @@
           <t>QNDeLd21</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A3YJH5zr</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gaines julian</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mupyf1oM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>godoy anibal</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>42SIX9sl</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>alba jordi</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4nPbkFeS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>farias facundo</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>drwnu3ZE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>freire nicolas</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>KrSC9Fhb</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gomez diego</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>vgOOdZbd</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>messi lionel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>KGSWnoI0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>leal randall</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>nBxbbXjd</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>robinson robbie</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>dUShzrBp</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>suarez luis</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>EkrhE4VR</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>moore shaquell</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>WYtXt0RH</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>shaffelburg jacob</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -730,10 +1384,26 @@
           <t>W0EiMxme</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Krqp3vSl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4j77gmDr</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ndenbe logan</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -744,6 +1414,20 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -751,20 +1435,58 @@
           <t>xbHaKGH7</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>O2OHmuib</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>chacon daniel</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nXphGKf9</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>stewart baynes kimani</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -772,20 +1494,66 @@
           <t>v3erq0f8</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t6eNizpa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>araujo miguel</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>COWIPrGB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>loria marvin</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p0fLP0ug</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>bacharach hugo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>jVJw0C0o</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>dotson hassani</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -793,20 +1561,90 @@
           <t>IgfnrK9E</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AVAn8mrG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>daniel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>l8BtS6uD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>brugman gaston</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Stw5HjsM</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>perez jonathan</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>GxVEgL1o</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>puig ricard</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>08UQE1DR</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>bThWSPHa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>costa vitor</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -818,16 +1656,62 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fRhphq6i</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>gasper chase</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>QJrUSjEf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>gutman andrew</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fqzwMb0n</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>salquist tobias</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CKcCpcKN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>shaqiri xherdan</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -835,10 +1719,26 @@
           <t>YyTMIXGq</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29H9TmUe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>adekugbe sam</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0MWvMpbP</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>schopf alessandro</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -849,6 +1749,20 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -870,6 +1784,20 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -891,6 +1819,20 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -912,6 +1854,20 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -933,6 +1889,20 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -954,6 +1924,20 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -975,6 +1959,20 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -996,6 +1994,20 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1017,6 +2029,20 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1038,6 +2064,20 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1059,6 +2099,20 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1080,6 +2134,20 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1101,6 +2169,20 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1122,6 +2204,20 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1143,6 +2239,20 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1164,6 +2274,20 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1185,6 +2309,20 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1206,6 +2344,20 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1227,6 +2379,20 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1248,6 +2414,20 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1269,6 +2449,20 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1290,6 +2484,20 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1311,6 +2519,20 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1332,6 +2554,20 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1353,6 +2589,20 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1374,6 +2624,20 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1395,6 +2659,20 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1416,6 +2694,20 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1437,6 +2729,20 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1458,6 +2764,20 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1479,6 +2799,20 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1500,6 +2834,20 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -431,135 +431,151 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_2</t>
+          <t>id_player_miss_away_3</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_2</t>
+          <t>player_name_miss_away_3</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_3</t>
+          <t>id_player_miss_away_4</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_3</t>
+          <t>player_name_miss_away_4</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_4</t>
+          <t>id_player_miss_away_5</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_4</t>
+          <t>player_name_miss_away_5</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_5</t>
+          <t>id_player_miss_away_6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_5</t>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_6</t>
+          <t>id_player_miss_away_7</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_6</t>
+          <t>player_name_miss_away_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>lEm6FVi5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lennon brooks</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>vPuxSnSS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>mosquera edwin</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nmEIaKrM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bush evan</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -580,184 +596,152 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fLPZURJf</t>
+          <t>GAfAmzTA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anunga brian</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ENyQYY5d</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>antley william</t>
-        </is>
-      </c>
+          <t>ketterer logan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GjDwWCMo</t>
+          <t>GY24D9os</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bartlett lucas allen</t>
+          <t>servania brandon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0892INjM</t>
+          <t>WSKByXG4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>birnbaum steven</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>pMh10sbj</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>canouse russell</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>U9y2jka5</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>hopkins jackson</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>A3YJH5zr</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>gaines julian</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Mupyf1oM</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>godoy anibal</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>KGSWnoI0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>leal randall</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>UXv2usbH</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>macnaughton lukas</t>
-        </is>
-      </c>
+          <t>spicer tyrese</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69kPHWm8</t>
+          <t>4nPbkFeS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>agyemang patrick</t>
+          <t>farias facundo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G8J0E6NO</t>
+          <t>drwnu3ZE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hagglund nick</t>
+          <t>freire nicolas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xtm44hb9</t>
+          <t>fRhphq6i</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>miazga matthew</t>
+          <t>gasper chase</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Qgy2DEEi</t>
+          <t>QJrUSjEf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nwobodo obinna</t>
+          <t>gutman andrew</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>QJXMi0b1</t>
+          <t>vgOOdZbd</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pinto malik</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>messi lionel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>nBxbbXjd</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>robinson robbie</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Y7GqEIyO</t>
+          <t>YBrWh9gH</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>junior urso</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>navarro federico</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CKcCpcKN</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>shaqiri xherdan</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>GAG3nyP6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>teran carlos</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -766,155 +750,267 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GxlXiF6D</t>
+          <t>rorJXVFH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halliday michael</t>
+          <t>chancalay tomas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rorJXVFH</t>
+          <t>bcUmtA2T</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>chancalay tomas</t>
+          <t>gil ignacio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>bcUmtA2T</t>
+          <t>8EjOd1bt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>gil ignacio</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>delgado patrickson</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G0FHIX1G</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ferreira jesus</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2JMpq78N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>musa petar</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ngsoZ62f</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>pomykal paxton</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ELzAby5L</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>velasco alan</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ABzjRFre</t>
+          <t>EHyj8Rwo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>blake andre</t>
+          <t>mitchell roald</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ghmdi8ej</t>
+          <t>lrm5HUGk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>bernardeschi federico</t>
+          <t>nealis sean</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GY24D9os</t>
+          <t>G8J0E6NO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>servania brandon</t>
+          <t>hagglund nick</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WSKByXG4</t>
+          <t>YHNlP88c</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>spicer tyrese</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chep7XVi</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ngoma serge</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2RlHwfAS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stroud peter</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Ewo9UCjb</t>
+          <t>xtm44hb9</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>leflore isaiah</t>
+          <t>miazga matthew</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>8643FysN</t>
+          <t>QJXMi0b1</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>uhre mikael</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>pinto malik</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>EeCZfvc1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>powell alvas</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>EmByTsz3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>yedlin deandre</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>b3GRSs53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GxlXiF6D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>halliday michael</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mwp1l15G</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>gray tayvon</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Qo2F3mDP</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>jones malachi</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>OUEkZ70a</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>o toole kevin</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tx4wbOZQ</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>perea andreas</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -925,65 +1021,65 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AuWO1Jom</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>czichos rafael</t>
-        </is>
-      </c>
+          <t>tS5WR1K9</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ewo9UCjb</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>leflore isaiah</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>fRhphq6i</t>
+          <t>A3YJH5zr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gasper chase</t>
+          <t>gaines julian</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>QJrUSjEf</t>
+          <t>Mupyf1oM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>gutman andrew</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fqzwMb0n</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>salquist tobias</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>GAG3nyP6</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>teran carlos</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>godoy anibal</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>KGSWnoI0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>leal randall</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UXv2usbH</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>macnaughton lukas</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -994,69 +1090,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>l8BtS6uD</t>
+          <t>On4D2kf7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brugman gaston</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>zPaFQZT7</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>arriola paul</t>
-        </is>
-      </c>
+          <t>driussi sebastian</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8EjOd1bt</t>
+          <t>2Hk6Qxu3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>delgado patrickson</t>
+          <t>byrne nathan</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G0FHIX1G</t>
+          <t>Y7GqEIyO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ferreira jesus</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2BYxcCoI</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>geovane jesus</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ngsoZ62f</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>pomykal paxton</t>
-        </is>
-      </c>
+          <t>junior urso</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1065,21 +1137,13 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ELzAby5L</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>velasco alan</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1094,50 +1158,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>b7DGETog</t>
+          <t>f9lQiP3d</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>escobar franco</t>
+          <t>boxall michael</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SdBJUCMo</t>
+          <t>AVAn8mrG</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>quinones nelson</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>daniel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dUHOzpD6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>irwin clinton</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4jJNjzW1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>trapp wil</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>dUHOzpD6</t>
+          <t>08UQE1DR</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>irwin clinton</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4jJNjzW1</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>trapp wil</t>
-        </is>
-      </c>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1148,21 +1228,29 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29H9TmUe</t>
+          <t>Krqp3vSl</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>adekugbe sam</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4j77gmDr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ndenbe logan</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -1171,16 +1259,8 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>SbZcWdsA</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>blackmon tristan</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1193,128 +1273,128 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EHyj8Rwo</t>
+          <t>O2OHmuib</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mitchell roald</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>O2OHmuib</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>chacon daniel</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CAuDyvgB</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>arango cristian</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>APPpO179</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>bonilla jose</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Chep7XVi</t>
+          <t>0laOLfLr</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>ngoma serge</t>
+          <t>holt erik</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2RlHwfAS</t>
+          <t>Oz0bfR4G</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>stroud peter</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+          <t>katranis alexandros</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4Sow7kS0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>luna diego</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>fZM0WV7l</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>ruiz pablo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>8dMNjLjD</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>silva marcelo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>APPpO179</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>bonilla jose</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>COWIPrGB</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>loria marvin</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>vNmJIcsd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0laOLfLr</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>holt erik</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>fZM0WV7l</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>ruiz pablo</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>8dMNjLjD</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>silva marcelo</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1323,37 +1403,29 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nmEIaKrM</t>
+          <t>SbZcWdsA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bush evan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>AymTlL8c</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
+          <t>blackmon tristan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M9UPk5L5</t>
+          <t>SdBJUCMo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tillman timothy</t>
+          <t>quinones nelson</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1376,73 +1448,57 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CSKL6HMI</t>
+          <t>l8BtS6uD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bassong zohran</t>
+          <t>brugman gaston</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AVAn8mrG</t>
+          <t>ETvClz3P</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>daniel</t>
+          <t>cerrillo edwin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>v5gGA3R2</t>
+          <t>U3WGsjPA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>marcinkowski jt</t>
+          <t>chara diego</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>08UQE1DR</t>
+          <t>COWIPrGB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ricketts jamar</t>
+          <t>loria marvin</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Krqp3vSl</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>ford kortne</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>4j77gmDr</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ndenbe logan</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_player_next.xlsx
@@ -425,118 +425,568 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:DI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_6</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_7</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
         </is>
       </c>
     </row>
@@ -548,50 +998,428 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>M3Uze1K2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>guzan brad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>lEm6FVi5</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>lennon brooks</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4U2YRBhO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>williams derrick</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vPRl0Icq</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gregersen stian</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>QmYwykMP</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hernandez ronald</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>dAeQdaOl</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>muyumba tristan</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vPHmMOvg</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>fortune ajani</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Mc2UiGHB</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>slisz bartosza</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SEHVGTmg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>lobjanidze saba</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ULIarm52</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thiare jamal</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>jLbdGy1R</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>silva xande</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>hGBjyLfE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>hagen nicholas</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>zk4qsEuM</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>moreira steven</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>QganPGYI</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>camacho rudy</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>f5qxQepJ</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>cheberko yevgen</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>AqWyTfI5</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>farsi mohamed</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>rH3tj2lb</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>zawadzki sean</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>A9cyouqp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>matan alexandru</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Y7TZabC7</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>arfsten maximilian</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>nmxk6R3j</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ramirez christian</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>f3AIj6Gd</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>rossi diego</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>65KF7LTO</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>cucho hernandez</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>8xa2tgyo</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>abram luis</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2BzWQRsG</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>amador pedro miguel santos</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>A5qnVvGT</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>cohen josh</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>O8hSmb4T</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>edwards matthew</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>r1ZFqEYf</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>mccarty dax</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>vPuxSnSS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>mosquera edwin</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>WSg3ZNRK</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>rios daniel</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Cj6yFHA1</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>wolff tyler</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>IVdZK6M8</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>amundsen malte</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>U3UI3wS3</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>jackson aziel</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>KMj0M58F</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>johnson cole</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>A70Jf46M</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>jones derrick</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>SOGHjAs1</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>nagbe darlington</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>dzTXj2Mu</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>russell rowe jacen</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>YueP3mZg</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>sands will</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>lMqsisyG</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>yeboah yaw</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>nmEIaKrM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>bush evan</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -601,50 +1429,468 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>M9zBEjDs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sirois jonathan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0l5tduvR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>waterman joel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UmKMb5IL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>alvarez fernando</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GxeZPglE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sosa joaquin</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4YJ3ucPB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ruan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>63QJMufq</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>piette samuel</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>hCaK2R0o</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>choiniere mathieu</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>zDdlwQJ0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>edwards raheem</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>nu3nYaUJ</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vilsaint jules anthony</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>A5aLmv3S</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>lassiter ariel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>tfzJeW8h</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>martinez josef</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>bRSLQpm3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>johnson sean</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>S29QRgLo</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>gomis nickseon</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>z3epw0ga</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>o neill shane</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Yk1IUOBm</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>petretta raoul</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Ghmdi8ej</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>bernardeschi federico</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>CGI0s8Kj</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>longstaff matthew</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>QNVzA0WJ</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>thompson kosi</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>nT1BbXIh</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>laryea richie</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>KtKzNinp</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>osorio jonathan</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>6qUE0AeN</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>insigne lorenzo</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>E7o31oTD</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>owusu prince</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>hfSJRB5U</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>breza sebastian</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>I7xyHiFB</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>coccaro matias</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>xA02MROI</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>corbo gabriele</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>YZqwyK64</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>duke bryce</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>pYuWxIRg</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>iliadis ilias</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4fY0EIz8</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>opoku kwadwo</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>ALAGXH2B</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>saliba nathan</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>KGKRFdYJ</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>sanusi ibrahim</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>jagUidH4</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>etienne derick</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>zwOGJAV1</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>flores deybi</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>Yo7zAd0f</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>franklin kobe</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>p48dwOiT</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>luka gavran</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>UD0q8zV6</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>kerr deandre</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>AH6Dnzt9</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>long kevin</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>QZkWVPb4</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>mabika aime</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>rD6gr7yH</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>marshall rutty jahkeele</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>GY24D9os</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>servania brandon</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>OtUVLhLE</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>wanyama victor</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>xAK6V1ci</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>rosted sigurd</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>GAfAmzTA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>ketterer logan</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GY24D9os</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>servania brandon</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>UPOhwmAe</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>lappalainen lassi</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>WSKByXG4</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>spicer tyrese</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -654,98 +1900,516 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>vqw5aA54</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>callender drake</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>b1z41bWo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>weigandt marcelo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4pT7GbXj</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>aviles tomas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CU4pL3ue</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>busquets sergio</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>42SIX9sl</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>alba jordi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>zujWmxCn</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>redondo federico</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>OQNq36tC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bright yannick</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>OMbO44MM</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>rojas matias</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>rV3HgSkh</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>gressel julian</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>dUShzrBp</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>suarez luis</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>lbkZFpih</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>taylor robert</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>n79WXocj</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>brady chris</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>fagAWisc</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>souquet arnaud</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>W4J0GcZ4</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>omsberg wyatt</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>AuWO1Jom</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>czichos rafael</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2mWA9Y4H</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>arigoni allan</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2wPfQs28</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>herbers fabian</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>vc66Seae</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>acosta kellyn</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>4MkmBF09</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>gimenez gaston</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>hKGJC09T</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>gutierrez brian</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>z31sIFlM</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>haile selassie maren</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>EuZGz6mD</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>cuypers hugo</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>KUlXbpuK</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>allen noah</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>ltO3zYt1</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>campana leonardo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>KrwRQeq9</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>dos santos cj</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>CSNYauv4</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>fray ian</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>hprJvV7e</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>leonardo afonso</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>IwLMUvpl</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>negri franco</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>d2xu7eXs</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>ruiz david</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>M3Eg5vg9</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>sailor ryan</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Ug6FFtjG</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>barlow tom</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>CMEMk4l7</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>casas javier</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>dWTqQgRG</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>dean jr robert jonathan</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>dzmQbSaB</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>koutsias georgios</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Y3fj7Vhj</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>mueller chris</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>nX0UykbH</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>pineda mauricio</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>EX7msl6s</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>reynolds justin</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>8W6bELrN</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>richey spencer</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>fRhphq6i</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>gasper chase</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>6k5Ps8Em</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>sunderland lawson</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>fqzwMb0n</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>salquist tobias</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>4nPbkFeS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>farias facundo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>drwnu3ZE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>freire nicolas</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>fRhphq6i</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>gasper chase</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>QJrUSjEf</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>gutman andrew</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>ARaUcfV8</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>kryvtsov sergey</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
         <is>
           <t>vgOOdZbd</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>messi lionel</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>nBxbbXjd</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>robinson robbie</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>YBrWh9gH</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>navarro federico</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>CKcCpcKN</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>shaqiri xherdan</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>GAG3nyP6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>teran carlos</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -755,90 +2419,564 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>t2qaKiy1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ivacic aljaz</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>G6fhkE8g</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bye brandon</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>UoFEFxwC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kessler henry</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rgEPHjOC</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>arreaga xavier</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>r55LmW9c</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>miller peyton</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vDPZngKJ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>polster matt</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GAO1JDD7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>kaye mark</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>GUqdXgyQ</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>bajraktarevic esmir</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>tdzmBBpt</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>harkes ian</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>G4sqpfJn</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>mcnamara thomas</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>nHUd7ayo</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>wood bobby</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>QZUlDAhp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>paes maarten</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>UBJmVfdm</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>junqua sam</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>CpvYfWnT</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ibeagha sebastian</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>lnWs7qNJ</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>nkosi tafari</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>b7khARQH</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>farfan marco</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>dftXOTEE</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lletget sebastian</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>MqeBl5KD</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>sainte carl</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2ZREE4mC</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>ntsabeleng tsiki</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>zPaFQZT7</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>arriola paul</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>httabn7M</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>farrington logan</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>UgaTUneE</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>kamungo bernard</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>lOgLaOqB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>edwards earl</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>pfMI4LWA</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>farrell andrew</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>WIRaVUHM</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>fry malcolm</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>x8DF5hdR</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>lima nick</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>6JhyNld6</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>marcos dias</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4Ax57CjI</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>mensah jonathan</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>WGKzip6I</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>panayotou jack</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>jqg8GNsP</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>romney david</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>OMnknAig</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>ansah eugene</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>4CqLDV6H</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>carrera antonio</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>KQxwOHcP</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>endeley herbert</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>rB26jIhb</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>gonzalez omar</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0Wt2xH9a</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>korca amet</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>zZrA9hiI</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>ramirez anthony</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>MBluxjVo</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>sutarik scott</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>xfCyEHq2</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>sealy dante</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>8EjOd1bt</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>delgado patrickson</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>Me4woTz5</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>spaulding ryan</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>fP18CT0m</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>twumasi emmanuel</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>hfGr3JtE</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>boateng ema</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>8KDkbY05</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>borrero dylan</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>G0FHIX1G</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>ferreira jesus</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>zkeO5AoD</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>buck noel</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>rorJXVFH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>chancalay tomas</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>W8ixgd70</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>gil carles</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>6ZmchPft</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>fraser liam</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>2BYxcCoI</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>geovane jesus</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>INTB796M</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>illarramendi asier</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
         <is>
           <t>bcUmtA2T</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>gil ignacio</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>8EjOd1bt</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>delgado patrickson</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>G0FHIX1G</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ferreira jesus</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2BYxcCoI</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>geovane jesus</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>bgp40b4S</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>jones dejuan</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>AeAZMqTq</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>vrioni giacomo</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
         <is>
           <t>2JMpq78N</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>musa petar</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>ngsoZ62f</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="DG5" t="inlineStr">
         <is>
           <t>pomykal paxton</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>ELzAby5L</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>velasco alan</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -848,106 +2986,508 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>U1vy4HGk</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carlos coronel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2opOliMF</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nealis dylan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rXSckKil</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>reyes andres</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>21LF2F5n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>eile noah</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jkAB9GIq</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>duncan kyle</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AwQIIHlp</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>harper cameron</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8lSe4DC8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>donkor ronald</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>M3OWSmEK</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>edelman daniel</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S88XrqYl</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>carmona wikelman</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>hfxD47ea</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>morgan lewis</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>r9KSzxIr</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>elias manoel</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>65qMcSsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>celentano roman</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>EmByTsz3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>yedlin deandre</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Ac0f6aUi</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>murphy ian</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>CM9lhfg0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>keller kipp</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>xSjv8o7m</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>kubo yuya</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Qgy2DEEi</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>nwobodo obinna</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Wb24z4qm</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>bucha pavel</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>x4GDtQAg</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>halsey bret</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>SYf84XxQ</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>valenzuela gerado</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>nurCNCMA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>santos sergio</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>bgmn5guC</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>kelsy kevin</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>6k6rtKui</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>burke cory</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>61JmbCV4</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>estrela bento</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kx11bv9D</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>gjengaar dennis</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>lCyxppgD</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>hall julian</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>I7hHvjo8</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>meara ryan</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>CKmY1Xij</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>o connor aidan</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>jampKll4</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>sserwadda steven</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>tCiyx4fP</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>valencia omar</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>UHAYgN9J</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>acosta luciano</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>8vwLD9Pk</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>aghedo london</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>Ew6ZM870</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>asad yamil</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>29yL8IQ9</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>baird corey</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>KjuaVo0b</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>boupendza aaron</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>hxvYvgmQ</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>foster isaiah</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>6q7PrXhp</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>louro evan</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>CERONUR9</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>orellano luca</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>G8J0E6NO</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>hagglund nick</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>r98Hclis</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>vanzeir dante</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>QJXMi0b1</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>pinto malik</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>IehILnUA</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>forsberg emil</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>EHyj8Rwo</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>mitchell roald</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>YHNlP88c</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>kann alec</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
         <is>
           <t>lrm5HUGk</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>nealis sean</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>G8J0E6NO</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>hagglund nick</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>YHNlP88c</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>kann alec</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>Chep7XVi</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>ngoma serge</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>2RlHwfAS</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>stroud peter</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>xtm44hb9</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>miazga matthew</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>QJXMi0b1</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>pinto malik</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>EeCZfvc1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>powell alvas</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>EmByTsz3</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>yedlin deandre</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -957,66 +3497,460 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Ik9rz2Bn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gallese pedro</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bBmS5UX8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thorhallsson dagur</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>t65vhYRg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>schlegel rodrigo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8OM9Vfod</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>jansson robin</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6eXjEYkT</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>rafael santos</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>lOFDt82b</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>araujo cesar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>MN3tNIu1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>cartagena wilder</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>zLUoizhj</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ojeda martin</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>xjFz7K56</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>lodeiro nicolas</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2wLx0Osd</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>angulo ivan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>KCeKofNN</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>enrique ramiro</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>QmlhGCEq</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>freese matthew</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dYQXlhHM</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>ilenic mitja</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>WUxTggeR</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>martins thiago</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>faYXGFs7</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>risa birk</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>MoLN8Da1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>mcfarlane christian</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>4vVyDTKB</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>parks keaton</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0YOF6nEU</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>sands james</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>zVcqrarp</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>haak justin</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>QBC2xYxL</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>wolf hannes</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>zTIFXjy2</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>martinez alonso</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>6NagVF8Q</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>rodriguez santiago</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>lGn3Qr31</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>brekalo david</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4MsxRhmb</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>felipe martins</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>xxEtrKMD</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>freeman alexander</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>p8fMKT2U</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>kocevski jeorgio</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>CzMMXwgt</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>lynn jack</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>ltpb2uSG</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>muriel luis</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>ncdGec7l</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>otero javier</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0Mh1aQx6</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>smith kyle</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>KfGlrRKc</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>bakrar monsef</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>p2EGxXFg</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>barraza luis</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>hfXWRScD</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>fernandez julian</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>Mwp1l15G</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>gray tayvon</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>byM5LeL9</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>mijatovic jovan</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>AmR0hx1i</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>moralez maximiliano</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>Cz48tqxd</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>ojeda axel</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>2JjMjHFd</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>talles magno</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>Qo2F3mDP</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>jones malachi</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>lhAqDO8D</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>torres facundo</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>UyiqLYVE</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>tanasijevic strahinja</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>GxlXiF6D</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>halliday michael</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mwp1l15G</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>gray tayvon</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Qo2F3mDP</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>jones malachi</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>OUEkZ70a</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>o toole kevin</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>tx4wbOZQ</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>perea andreas</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1026,66 +3960,460 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>ABzjRFre</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>blake andre</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>08Tn3g3J</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mbaizo olivier</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>QyCyxm0g</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>glesnes jakob</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>l0UioTxt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lowe damion</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O6htidEe</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>wagner kai</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>8tHxTMze</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>martinez jose</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>tlilbW9M</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>sullivan quinn</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>pK1XzKbU</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>flach leon</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>dlj9zaWb</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>gazdag daniel</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>259hPT4F</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>baribo tai</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>8643FysN</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>uhre mikael</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>pWyXltXM</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>willis joe</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>EkrhE4VR</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>moore shaquell</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>pGfsH28e</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>bauer josh</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>6F1piUu8</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>kallman brent</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Q9DK6zoi</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>washinghton taylor</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>fLPZURJf</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>anunga brian</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>SWznQDvn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>davis sean</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>K6P22oZn</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>muyl alex</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>4G68jNi8</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>mukhtar hany</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>WYtXt0RH</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>shaffelburg jacob</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Q1pKUFNf</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>ajago forster</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>jJ0Bn0VE</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>adeniran samuel</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>UsBqE6t9</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>bedoya alejandro</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>MBaUW69d</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>bueno jesus</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>EFptvtls</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>donovan chris</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>8CN7Nng2</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>elliott jack</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>I17X8gpH</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>rafanello jeremy</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>fyVC7jve</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>rick andrew</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>zBzH8JUb</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>sullivan cavan</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>MsoRu1wq</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>bunbury teal</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>Mupyf1oM</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>godoy anibal</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>I1vgdBJL</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>jones isaiah</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>xnWjT5xI</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>lovitz daniel</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>4fTRivtk</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>maher jack</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>Kb60n3mi</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>panicco elliot</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>W6OKBZvA</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>sejdic amar</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>fecCS155</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>skinner joseph</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>A3YJH5zr</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>gaines julian</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>nPUVWwa4</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>westfield francis</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>Ewo9UCjb</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>leflore isaiah</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>A3YJH5zr</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>gaines julian</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Mupyf1oM</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>godoy anibal</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>KGSWnoI0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>leal randall</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr">
         <is>
           <t>UXv2usbH</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>macnaughton lukas</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1093,38 +4421,14 @@
           <t>h29zRLZF</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>On4D2kf7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>driussi sebastian</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2Hk6Qxu3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>byrne nathan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Y7GqEIyO</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>junior urso</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1139,6 +4443,120 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>2Hk6Qxu3</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>byrne nathan</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>On4D2kf7</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>driussi sebastian</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>Y7GqEIyO</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>junior urso</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1146,76 +4564,20 @@
           <t>QF7rPa4S</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>p0fLP0ug</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bacharach hugo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>f9lQiP3d</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>boxall michael</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AVAn8mrG</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>daniel</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>v5gGA3R2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>marcinkowski jt</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dUHOzpD6</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>irwin clinton</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4jJNjzW1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>trapp wil</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>08UQE1DR</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>ricketts jamar</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1224,6 +4586,152 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>AVAn8mrG</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>daniel</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>p0fLP0ug</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>bacharach hugo</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>f9lQiP3d</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>boxall michael</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>v5gGA3R2</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>marcinkowski jt</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>dUHOzpD6</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>irwin clinton</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>4jJNjzW1</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>trapp wil</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>08UQE1DR</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>ricketts jamar</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1231,26 +4739,10 @@
           <t>nP8vQukM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Krqp3vSl</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ford kortne</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4j77gmDr</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ndenbe logan</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -1269,6 +4761,112 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>Krqp3vSl</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>ford kortne</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>4j77gmDr</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>ndenbe logan</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1276,92 +4874,182 @@
           <t>69kBKJCq</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>O2OHmuib</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>chacon daniel</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CAuDyvgB</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>arango cristian</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>APPpO179</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>bonilla jose</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>CAuDyvgB</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>arango cristian</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>O2OHmuib</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>chacon daniel</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>APPpO179</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>bonilla jose</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr">
         <is>
           <t>0laOLfLr</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>holt erik</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>Oz0bfR4G</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>katranis alexandros</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>4Sow7kS0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>luna diego</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr">
         <is>
           <t>fZM0WV7l</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="DE12" t="inlineStr">
         <is>
           <t>ruiz pablo</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="DF12" t="inlineStr">
         <is>
           <t>8dMNjLjD</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="DG12" t="inlineStr">
         <is>
           <t>silva marcelo</t>
         </is>
       </c>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1373,16 +5061,8 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AymTlL8c</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>dellavalle lorenzo</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1399,6 +5079,104 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>AymTlL8c</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>dellavalle lorenzo</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1406,28 +5184,12 @@
           <t>MHXbihN8</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SbZcWdsA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>blackmon tristan</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SdBJUCMo</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>quinones nelson</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1444,6 +5206,112 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>SdBJUCMo</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>quinones nelson</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>SbZcWdsA</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>blackmon tristan</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1451,46 +5319,14 @@
           <t>p0lFJwSk</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>l8BtS6uD</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>brugman gaston</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ETvClz3P</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>cerrillo edwin</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>U3WGsjPA</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>chara diego</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>COWIPrGB</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>loria marvin</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1505,6 +5341,128 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>U3WGsjPA</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>chara diego</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>l8BtS6uD</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>brugman gaston</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>ETvClz3P</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>cerrillo edwin</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>COWIPrGB</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>loria marvin</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
